--- a/Configs/GameConfig/Datas/道具表.xlsx
+++ b/Configs/GameConfig/Datas/道具表.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20150" windowHeight="17080" activeTab="1"/>
+    <workbookView windowHeight="17680" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="道具表" sheetId="1" r:id="rId1"/>
-    <sheet name="货币表" sheetId="2" r:id="rId2"/>
-    <sheet name="获取途径表" sheetId="3" r:id="rId3"/>
+    <sheet name="道具转化表" sheetId="4" r:id="rId2"/>
+    <sheet name="货币表" sheetId="2" r:id="rId3"/>
+    <sheet name="获取途径表" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -83,21 +84,12 @@
     <t>quality</t>
   </si>
   <si>
-    <t>exchange_list</t>
-  </si>
-  <si>
-    <t>test</t>
+    <t>itemType</t>
   </si>
   <si>
     <t>getways</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>num</t>
-  </si>
-  <si>
     <t>##type</t>
   </si>
   <si>
@@ -107,10 +99,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>(list#sep=;),item.ItemExchange</t>
-  </si>
-  <si>
-    <t>item.ItemExchange</t>
+    <t>item.ItemType</t>
   </si>
   <si>
     <t>int#ref=item.TbGetWay</t>
@@ -123,9 +112,6 @@
   </si>
   <si>
     <t>s</t>
-  </si>
-  <si>
-    <t>c,s</t>
   </si>
   <si>
     <t>##</t>
@@ -163,91 +149,127 @@
     <t>品质</t>
   </si>
   <si>
+    <t>道具类型</t>
+  </si>
+  <si>
+    <t>获取途径</t>
+  </si>
+  <si>
+    <t>发型</t>
+  </si>
+  <si>
+    <t>初始发型</t>
+  </si>
+  <si>
+    <t>Goods</t>
+  </si>
+  <si>
+    <t>外套</t>
+  </si>
+  <si>
+    <t>初始外套</t>
+  </si>
+  <si>
+    <t>上衣</t>
+  </si>
+  <si>
+    <t>初始上衣</t>
+  </si>
+  <si>
+    <t>裙子</t>
+  </si>
+  <si>
+    <t>初始下装</t>
+  </si>
+  <si>
+    <t>袜子</t>
+  </si>
+  <si>
+    <t>初始袜子</t>
+  </si>
+  <si>
+    <t>鞋子</t>
+  </si>
+  <si>
+    <t>初始鞋子</t>
+  </si>
+  <si>
+    <t>发饰</t>
+  </si>
+  <si>
+    <t>初始发饰</t>
+  </si>
+  <si>
+    <t>中秋节发饰</t>
+  </si>
+  <si>
+    <t>中秋节鞋子</t>
+  </si>
+  <si>
+    <t>礼包</t>
+  </si>
+  <si>
+    <t>中秋节礼包</t>
+  </si>
+  <si>
+    <t>isApplyImmediately</t>
+  </si>
+  <si>
+    <t>exchange_list</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>num</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>(list#sep=;),item.ItemExchange</t>
+  </si>
+  <si>
+    <t>item.ItemExchange</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>兑换是否立即生效</t>
+  </si>
+  <si>
     <t>道具兑换配置</t>
   </si>
   <si>
-    <t>获取途径</t>
-  </si>
-  <si>
-    <t>发型</t>
-  </si>
-  <si>
-    <t>初始发型</t>
-  </si>
-  <si>
     <t>10001,2;10002,3</t>
   </si>
   <si>
-    <t>外套</t>
-  </si>
-  <si>
-    <t>初始外套</t>
-  </si>
-  <si>
     <t>10001,2;10002,4</t>
   </si>
   <si>
-    <t>上衣</t>
-  </si>
-  <si>
-    <t>初始上衣</t>
-  </si>
-  <si>
     <t>10001,2;10002,5</t>
   </si>
   <si>
-    <t>裙子</t>
-  </si>
-  <si>
-    <t>初始下装</t>
-  </si>
-  <si>
     <t>10001,2;10002,6</t>
   </si>
   <si>
-    <t>袜子</t>
-  </si>
-  <si>
-    <t>初始袜子</t>
-  </si>
-  <si>
     <t>10001,2;10002,7</t>
   </si>
   <si>
-    <t>鞋子</t>
-  </si>
-  <si>
-    <t>初始鞋子</t>
-  </si>
-  <si>
     <t>10001,2;10002,8</t>
   </si>
   <si>
-    <t>发饰</t>
-  </si>
-  <si>
-    <t>初始发饰</t>
-  </si>
-  <si>
     <t>10001,2;10002,9</t>
   </si>
   <si>
-    <t>中秋节发饰</t>
-  </si>
-  <si>
     <t>10001,2;10002,10</t>
   </si>
   <si>
-    <t>中秋节鞋子</t>
-  </si>
-  <si>
     <t>10001,2;10002,11</t>
-  </si>
-  <si>
-    <t>礼包</t>
-  </si>
-  <si>
-    <t>中秋节礼包</t>
   </si>
   <si>
     <t>10001,2;10002,12</t>
@@ -1030,28 +1052,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1402,22 +1424,19 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="9.29090909090909" style="5" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="9" customWidth="1"/>
+    <col min="2" max="2" width="6.71818181818182" style="15" customWidth="1"/>
     <col min="3" max="3" width="27.1818181818182" style="5" customWidth="1"/>
     <col min="4" max="4" width="22" style="5" customWidth="1"/>
-    <col min="5" max="6" width="23.5454545454545" style="5" customWidth="1"/>
-    <col min="7" max="7" width="28.0090909090909" style="5" customWidth="1"/>
-    <col min="8" max="8" width="13.0090909090909" style="10" customWidth="1"/>
-    <col min="9" max="9" width="12.1818181818182" style="10" customWidth="1"/>
-    <col min="10" max="10" width="32.0909090909091" style="5" customWidth="1"/>
-    <col min="11" max="31" width="12.4363636363636" style="5" customWidth="1"/>
+    <col min="5" max="7" width="23.5454545454545" style="5" customWidth="1"/>
+    <col min="8" max="8" width="32.0909090909091" style="5" customWidth="1"/>
+    <col min="9" max="29" width="12.4363636363636" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:10">
+    <row r="1" ht="21.75" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1439,15 +1458,11 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:10">
+    </row>
+    <row r="2" ht="21.75" customHeight="1" spans="1:8">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,365 +1472,610 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" ht="21.75" customHeight="1" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1"/>
-    </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" ht="21.75" customHeight="1" spans="1:8">
+      <c r="A4" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="21.75" customHeight="1" spans="1:10">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="14"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" ht="22.5" customHeight="1" spans="1:10">
-      <c r="A5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" s="1"/>
-      <c r="H5" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" ht="21.75" customHeight="1" spans="1:10">
+    </row>
+    <row r="6" ht="21.75" customHeight="1" spans="1:8">
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F6" s="5">
         <v>1</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I6" s="16">
-        <v>2</v>
-      </c>
-      <c r="J6" s="5">
+      <c r="G6" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="21.75" customHeight="1" spans="1:10">
+    <row r="7" ht="21.75" customHeight="1" spans="1:8">
       <c r="B7" s="6">
         <v>10001</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I7" s="16">
-        <v>3</v>
-      </c>
-      <c r="J7" s="5">
+      <c r="G7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="21.75" customHeight="1" spans="1:10">
+    <row r="8" ht="21.75" customHeight="1" spans="1:8">
       <c r="B8" s="6">
         <v>10002</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F8" s="5">
         <v>3</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I8" s="16">
-        <v>4</v>
-      </c>
-      <c r="J8" s="5">
+      <c r="G8" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="5">
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="21.75" customHeight="1" spans="1:10">
+    <row r="9" ht="21.75" customHeight="1" spans="1:8">
       <c r="B9" s="6">
         <v>10003</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F9" s="5">
         <v>4</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="H9" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I9" s="16">
-        <v>5</v>
-      </c>
-      <c r="J9" s="5">
+      <c r="G9" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="21.75" customHeight="1" spans="1:10">
+    <row r="10" ht="21.75" customHeight="1" spans="1:8">
       <c r="B10" s="6">
         <v>10004</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F10" s="5">
         <v>5</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I10" s="16">
-        <v>6</v>
-      </c>
-      <c r="J10" s="5">
+      <c r="G10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="5">
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="21.75" customHeight="1" spans="1:10">
+    <row r="11" ht="21.75" customHeight="1" spans="1:8">
       <c r="B11" s="6">
         <v>10005</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F11" s="5">
         <v>5</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I11" s="16">
-        <v>7</v>
-      </c>
-      <c r="J11" s="5">
+      <c r="G11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="5">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="21.75" customHeight="1" spans="1:10">
+    <row r="12" ht="21.75" customHeight="1" spans="1:8">
       <c r="B12" s="6">
         <v>10006</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F12" s="5">
         <v>5</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I12" s="16">
-        <v>8</v>
-      </c>
-      <c r="J12" s="5">
+      <c r="G12" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="5">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="20.25" customHeight="1" spans="1:10">
+    <row r="13" ht="20.25" customHeight="1" spans="1:8">
       <c r="B13" s="6">
         <v>10007</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F13" s="5">
         <v>5</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="H13" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I13" s="16">
-        <v>9</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="G13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="14" ht="20.25" customHeight="1" spans="1:10">
+    <row r="14" ht="20.25" customHeight="1" spans="1:8">
       <c r="B14" s="6">
         <v>10008</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="F14" s="5">
         <v>5</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H14" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I14" s="16">
-        <v>10</v>
-      </c>
-      <c r="J14" s="5">
+      <c r="G14" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="5">
         <v>9</v>
       </c>
     </row>
-    <row r="15" ht="20.25" customHeight="1" spans="1:10">
+    <row r="15" ht="20.25" customHeight="1" spans="1:8">
       <c r="B15" s="6">
         <v>10009</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F15" s="5">
         <v>5</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="16">
-        <v>10001</v>
-      </c>
-      <c r="I15" s="16">
-        <v>11</v>
-      </c>
-      <c r="J15" s="5">
+      <c r="G15" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="5">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="H3:I3"/>
-  </mergeCells>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="28.1818181818182" customWidth="1"/>
+    <col min="3" max="3" width="32.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="41.1818181818182" customWidth="1"/>
+    <col min="5" max="5" width="24.0909090909091" customWidth="1"/>
+    <col min="6" max="6" width="37.9090909090909" customWidth="1"/>
+    <col min="7" max="7" width="14.5454545454545" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="10"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" s="13"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" ht="14.5" spans="1:7">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G6" s="14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="14.5" spans="1:7">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6">
+        <v>10001</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" ht="14.5" spans="1:7">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6">
+        <v>10002</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G8" s="14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" ht="14.5" spans="1:7">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6">
+        <v>10003</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" ht="14.5" spans="1:7">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6">
+        <v>10004</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F10" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" ht="14.5" spans="1:7">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6">
+        <v>10005</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G11" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" ht="14.5" spans="1:7">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6">
+        <v>10006</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G12" s="14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="14.5" spans="1:7">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6">
+        <v>10007</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G13" s="14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" ht="14.5" spans="1:7">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6">
+        <v>10008</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F14" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G14" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" ht="14.5" spans="1:7">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6">
+        <v>10009</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="14">
+        <v>10001</v>
+      </c>
+      <c r="G15" s="14">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F3:G3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H15"/>
@@ -1839,10 +2099,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -1861,27 +2121,27 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="3"/>
@@ -1893,22 +2153,22 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1919,14 +2179,14 @@
         <v>1</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="8">
         <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
@@ -1937,14 +2197,14 @@
         <v>2</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="6">
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -2011,7 +2271,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
@@ -2031,13 +2291,13 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2047,38 +2307,38 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2086,10 +2346,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2097,10 +2357,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2108,10 +2368,10 @@
         <v>3</v>
       </c>
       <c r="C8" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2119,10 +2379,10 @@
         <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2130,10 +2390,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2141,10 +2401,10 @@
         <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2152,10 +2412,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/道具表.xlsx
+++ b/Configs/GameConfig/Datas/道具表.xlsx
@@ -1759,7 +1759,7 @@
     <col min="2" max="2" width="28.1818181818182" customWidth="1"/>
     <col min="3" max="3" width="32.0909090909091" customWidth="1"/>
     <col min="4" max="4" width="41.1818181818182" customWidth="1"/>
-    <col min="5" max="5" width="24.0909090909091" customWidth="1"/>
+    <col min="5" max="5" width="58.1818181818182" customWidth="1"/>
     <col min="6" max="6" width="37.9090909090909" customWidth="1"/>
     <col min="7" max="7" width="14.5454545454545" customWidth="1"/>
   </cols>
